--- a/projmonit2.xlsx
+++ b/projmonit2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johnp\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johnp\Desktop\GitHub Repositories\city-planning-system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE7B60DE-30E8-489C-B22B-ACD23A584D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3909416C-3431-48B0-9C35-FA3407297A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="840" windowWidth="14340" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="60" yWindow="840" windowWidth="28680" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Non-Infrastructure Projects" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Project Monitoring / Status Report</t>
   </si>
@@ -65,9 +65,6 @@
   </si>
   <si>
     <t>Action Taken/ Recommendation</t>
-  </si>
-  <si>
-    <t>Action Taken / Recommendation</t>
   </si>
   <si>
     <t>Remarks</t>
@@ -170,7 +167,7 @@
       <name val="Century Gothic"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -189,8 +186,14 @@
         <bgColor rgb="FFB3E5A1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="34">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -439,7 +442,9 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
@@ -447,25 +452,55 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -475,62 +510,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
@@ -565,19 +544,6 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -605,7 +571,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -632,9 +598,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
@@ -642,27 +606,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -676,6 +625,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -899,50 +861,53 @@
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="4" max="6" width="15.42578125" customWidth="1"/>
+    <col min="4" max="5" width="15.42578125" customWidth="1"/>
+    <col min="6" max="6" width="19.5703125" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" customWidth="1"/>
+    <col min="15" max="15" width="20.85546875" customWidth="1"/>
     <col min="16" max="17" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="38" t="s">
+      <c r="C1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="39"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="30"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="3"/>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="41"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="32"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
@@ -965,7 +930,7 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -984,75 +949,73 @@
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="27" t="s">
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="27" t="s">
+      <c r="K5" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="L5" s="27" t="s">
+      <c r="L5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="M5" s="27" t="s">
+      <c r="M5" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="27" t="s">
+      <c r="N5" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="O5" s="27" t="s">
+      <c r="O5" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="P5" s="29" t="s">
+      <c r="P5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q5" s="39"/>
+    </row>
+    <row r="6" spans="1:17" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
       <c r="F6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="H6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="I6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="30"/>
-      <c r="Q6" s="30"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="34"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="34"/>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="39"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
@@ -1071,444 +1034,444 @@
       <c r="N7" s="12"/>
       <c r="O7" s="12"/>
       <c r="P7" s="13"/>
-      <c r="Q7" s="14"/>
+      <c r="Q7" s="39"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="18"/>
-      <c r="Q8" s="19"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="39"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="18"/>
-      <c r="Q9" s="19"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="39"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="18"/>
-      <c r="Q10" s="19"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="39"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="18"/>
-      <c r="Q11" s="19"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="39"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="18"/>
-      <c r="Q12" s="19"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="39"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="18"/>
-      <c r="Q13" s="19"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="39"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="18"/>
-      <c r="Q14" s="19"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="16"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="39"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="18"/>
-      <c r="Q15" s="19"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="39"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="18"/>
-      <c r="Q16" s="19"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="39"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="18"/>
-      <c r="Q17" s="19"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16"/>
+      <c r="O17" s="16"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="39"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="18"/>
-      <c r="Q18" s="19"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="16"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="39"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="18"/>
-      <c r="Q19" s="19"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="39"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="17"/>
-      <c r="N20" s="17"/>
-      <c r="O20" s="17"/>
-      <c r="P20" s="18"/>
-      <c r="Q20" s="19"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="39"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="17"/>
-      <c r="O21" s="17"/>
-      <c r="P21" s="18"/>
-      <c r="Q21" s="19"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
+      <c r="N21" s="16"/>
+      <c r="O21" s="16"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="39"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="17"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="18"/>
-      <c r="Q22" s="19"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="16"/>
+      <c r="N22" s="16"/>
+      <c r="O22" s="16"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="39"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="17"/>
-      <c r="O23" s="17"/>
-      <c r="P23" s="18"/>
-      <c r="Q23" s="19"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="16"/>
+      <c r="L23" s="16"/>
+      <c r="M23" s="16"/>
+      <c r="N23" s="16"/>
+      <c r="O23" s="16"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="39"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="17"/>
-      <c r="O24" s="17"/>
-      <c r="P24" s="18"/>
-      <c r="Q24" s="19"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+      <c r="M24" s="16"/>
+      <c r="N24" s="16"/>
+      <c r="O24" s="16"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="39"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="17"/>
-      <c r="P25" s="18"/>
-      <c r="Q25" s="19"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
+      <c r="M25" s="16"/>
+      <c r="N25" s="16"/>
+      <c r="O25" s="16"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="39"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-      <c r="N26" s="17"/>
-      <c r="O26" s="17"/>
-      <c r="P26" s="18"/>
-      <c r="Q26" s="19"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+      <c r="M26" s="16"/>
+      <c r="N26" s="16"/>
+      <c r="O26" s="16"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="39"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17"/>
-      <c r="O27" s="17"/>
-      <c r="P27" s="18"/>
-      <c r="Q27" s="19"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="16"/>
+      <c r="N27" s="16"/>
+      <c r="O27" s="16"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="39"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
-      <c r="N28" s="17"/>
-      <c r="O28" s="17"/>
-      <c r="P28" s="18"/>
-      <c r="Q28" s="19"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="16"/>
+      <c r="O28" s="16"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="39"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="17"/>
-      <c r="P29" s="18"/>
-      <c r="Q29" s="19"/>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C29" s="14"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="16"/>
+      <c r="K29" s="16"/>
+      <c r="L29" s="16"/>
+      <c r="M29" s="16"/>
+      <c r="N29" s="16"/>
+      <c r="O29" s="16"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="39"/>
+    </row>
+    <row r="30" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="22"/>
-      <c r="L30" s="22"/>
-      <c r="M30" s="22"/>
-      <c r="N30" s="22"/>
-      <c r="O30" s="22"/>
-      <c r="P30" s="23"/>
-      <c r="Q30" s="24"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="20"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="20"/>
+      <c r="P30" s="21"/>
+      <c r="Q30" s="39"/>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
@@ -1531,8 +1494,8 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
-      <c r="B32" s="25" t="s">
-        <v>19</v>
+      <c r="B32" s="22" t="s">
+        <v>18</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
@@ -1546,16 +1509,16 @@
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
-      <c r="O32" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="P32" s="25"/>
+      <c r="O32" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="P32" s="22"/>
       <c r="Q32" s="2"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
-      <c r="B33" s="25" t="s">
-        <v>21</v>
+      <c r="B33" s="22" t="s">
+        <v>20</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -1569,15 +1532,15 @@
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
       <c r="O33" s="2"/>
-      <c r="P33" s="26" t="s">
-        <v>22</v>
+      <c r="P33" s="23" t="s">
+        <v>21</v>
       </c>
       <c r="Q33" s="2"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
-      <c r="B34" s="25" t="s">
-        <v>23</v>
+      <c r="B34" s="22" t="s">
+        <v>22</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -1634,14 +1597,13 @@
       <c r="Q36" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="Q5:Q6"/>
+  <mergeCells count="13">
+    <mergeCell ref="P5:P6"/>
     <mergeCell ref="F5:I5"/>
     <mergeCell ref="C1:Q1"/>
     <mergeCell ref="C2:Q2"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="O5:O6"/>
-    <mergeCell ref="P5:P6"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="D5:D6"/>
